--- a/measurements/31/Filled_2D_sections/axial/week31_axial_Batch_Allmarks.xlsx
+++ b/measurements/31/Filled_2D_sections/axial/week31_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,102 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +596,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.660618679357526</v>
+        <v>3682.426303854875</v>
       </c>
       <c r="D2" t="n">
-        <v>17.75458924944808</v>
+        <v>346.6372186797005</v>
       </c>
       <c r="E2" t="n">
-        <v>13.15087444607805</v>
+        <v>256.7551677567618</v>
       </c>
       <c r="F2" t="n">
         <v>1.350069101659091</v>
@@ -525,24 +615,60 @@
         <v>0.3851177586221429</v>
       </c>
       <c r="H2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.238839285714286</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28.80394345238095</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.714353354978354</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.688548018292683</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.475323932926829</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.081935975609756</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>28.80394345238095</v>
+      </c>
+      <c r="N2" t="n">
+        <v>13.44308035714286</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.289434523809524</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.091145833333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4.762834821428571</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.238839285714286</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.761160714285714</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.511904761904762</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>9.48633254015467</v>
+      <c r="AG2" s="2" t="n">
+        <v>3615.992063492064</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +679,79 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.64098750743605</v>
+        <v>3674.943310657596</v>
       </c>
       <c r="D3" t="n">
-        <v>17.86888905850853</v>
+        <v>348.8687863804045</v>
       </c>
       <c r="E3" t="n">
-        <v>13.03555930823815</v>
+        <v>254.5037769703638</v>
       </c>
       <c r="F3" t="n">
-        <v>1.370780388933204</v>
+        <v>1.370780388933203</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3794340305968254</v>
+        <v>0.3794340305968255</v>
       </c>
       <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.189360119047619</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28.8578869047619</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.406063988095238</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.7609565548780488</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.478086890243902</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.119521722560976</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>28.8578869047619</v>
+      </c>
+      <c r="N3" t="n">
+        <v>14.85677083333333</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.828125</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.550595238095238</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.610863095238095</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.832961309523809</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.269345238095238</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.189360119047619</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>17.31211917603888</v>
+      <c r="AG3" s="2" t="n">
+        <v>337.9985172464734</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +762,79 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.64098750743605</v>
+        <v>3674.943310657596</v>
       </c>
       <c r="D4" t="n">
-        <v>17.86888905850853</v>
+        <v>348.8687863804045</v>
       </c>
       <c r="E4" t="n">
-        <v>13.03555930823815</v>
+        <v>254.5037769703638</v>
       </c>
       <c r="F4" t="n">
-        <v>1.370780388933204</v>
+        <v>1.370780388933203</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3794340305968254</v>
+        <v>0.3794340305968255</v>
       </c>
       <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.189360119047619</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28.8578869047619</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.406063988095238</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.7609565548780488</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.478086890243902</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.119521722560976</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>28.8578869047619</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14.85677083333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.828125</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.550595238095238</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.610863095238095</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.832961309523809</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.269345238095238</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.189360119047619</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>12.8002503870464</v>
+      <c r="AG4" s="2" t="n">
+        <v>249.9096504137629</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +845,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.609458655562166</v>
+        <v>3662.925170068027</v>
       </c>
       <c r="D5" t="n">
-        <v>18.05073889871923</v>
+        <v>352.4191880226135</v>
       </c>
       <c r="E5" t="n">
-        <v>13.00453306116709</v>
+        <v>253.8980264323098</v>
       </c>
       <c r="F5" t="n">
-        <v>1.38803437338482</v>
+        <v>1.388034373384819</v>
       </c>
       <c r="G5" t="n">
-        <v>0.370611437564123</v>
+        <v>0.3706114375641231</v>
       </c>
       <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.51264880952381</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.496310763888887</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.7967797256097561</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.511623475609756</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.154201600609756</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>29.51264880952381</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15.55617559523809</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.988095238095238</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6.03422619047619</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.659970238095238</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.509300595238095</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.917410714285714</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AG5" s="2" t="n">
         <v>1.352331711908505</v>
       </c>
     </row>
@@ -694,43 +928,79 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.609458655562166</v>
+        <v>3662.925170068027</v>
       </c>
       <c r="D6" t="n">
-        <v>18.05073889871923</v>
+        <v>352.4191880226135</v>
       </c>
       <c r="E6" t="n">
-        <v>13.00453306116709</v>
+        <v>253.8980264323098</v>
       </c>
       <c r="F6" t="n">
-        <v>1.38803437338482</v>
+        <v>1.388034373384819</v>
       </c>
       <c r="G6" t="n">
-        <v>0.370611437564123</v>
+        <v>0.3706114375641231</v>
       </c>
       <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.51264880952381</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.496310763888887</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.7967797256097561</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.511623475609756</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.154201600609756</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>29.51264880952381</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15.55617559523809</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.988095238095238</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6.03422619047619</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4.659970238095238</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.509300595238095</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.917410714285714</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.3982754432903774</v>
+      <c r="AG6" s="2" t="n">
+        <v>0.3982754432903775</v>
       </c>
     </row>
     <row r="7">
@@ -741,43 +1011,79 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.609458655562166</v>
+        <v>3662.925170068027</v>
       </c>
       <c r="D7" t="n">
-        <v>18.05073889871923</v>
+        <v>352.4191880226135</v>
       </c>
       <c r="E7" t="n">
-        <v>13.00453306116709</v>
+        <v>253.8980264323098</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38803437338482</v>
+        <v>1.388034373384819</v>
       </c>
       <c r="G7" t="n">
-        <v>0.370611437564123</v>
+        <v>0.3706114375641231</v>
       </c>
       <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.51264880952381</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.496310763888887</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.7967797256097561</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.511623475609756</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.154201600609756</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>29.51264880952381</v>
+      </c>
+      <c r="N7" t="n">
+        <v>15.55617559523809</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.988095238095238</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6.03422619047619</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4.659970238095238</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.509300595238095</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.917410714285714</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2</v>
+      <c r="AG7" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1094,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.595181439619274</v>
+        <v>3657.482993197279</v>
       </c>
       <c r="D8" t="n">
-        <v>17.33230367520961</v>
+        <v>338.3925955636161</v>
       </c>
       <c r="E8" t="n">
-        <v>12.95820386526061</v>
+        <v>252.9935040360405</v>
       </c>
       <c r="F8" t="n">
         <v>1.337554483277997</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4013751457154761</v>
+        <v>0.4013751457154762</v>
       </c>
       <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.35565476190476</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.980902777777779</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.7944931402439025</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.196265243902439</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.9953791920731707</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>23.35565476190476</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15.51153273809524</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.086681547619047</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.000744047619047</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.700520833333333</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.509300595238095</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.880208333333333</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.8142387576219512</v>
+      <c r="AG8" s="2" t="n">
+        <v>1.330915178571429</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1177,79 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.595181439619274</v>
+        <v>3657.482993197279</v>
       </c>
       <c r="D9" t="n">
-        <v>17.33230367520961</v>
+        <v>338.3925955636161</v>
       </c>
       <c r="E9" t="n">
-        <v>12.95820386526061</v>
+        <v>252.9935040360405</v>
       </c>
       <c r="F9" t="n">
         <v>1.337554483277997</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4013751457154761</v>
+        <v>0.4013751457154762</v>
       </c>
       <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.35565476190476</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.980902777777779</v>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.7944931402439025</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.196265243902439</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9953791920731707</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>23.35565476190476</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15.51153273809524</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.086681547619047</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.000744047619047</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.700520833333333</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.509300595238095</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.880208333333333</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.255659298780488</v>
+      <c r="AG9" s="2" t="n">
+        <v>24.51525297619047</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1260,79 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.595181439619274</v>
+        <v>3657.482993197279</v>
       </c>
       <c r="D10" t="n">
-        <v>17.33230367520961</v>
+        <v>338.3925955636161</v>
       </c>
       <c r="E10" t="n">
-        <v>12.95820386526061</v>
+        <v>252.9935040360405</v>
       </c>
       <c r="F10" t="n">
         <v>1.337554483277997</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4013751457154761</v>
+        <v>0.4013751457154762</v>
       </c>
       <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23.35565476190476</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.980902777777779</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.7944931402439025</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.196265243902439</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.9953791920731707</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>23.35565476190476</v>
+      </c>
+      <c r="N10" t="n">
+        <v>15.51153273809524</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.086681547619047</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.000744047619047</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.700520833333333</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.509300595238095</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.880208333333333</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.034949028201219</v>
+      <c r="AG10" s="2" t="n">
+        <v>6.00002352248446</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1343,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.532718619869126</v>
+        <v>3633.673469387755</v>
       </c>
       <c r="D11" t="n">
-        <v>17.20616775024228</v>
+        <v>335.9299417904445</v>
       </c>
       <c r="E11" t="n">
-        <v>12.77145135111925</v>
+        <v>249.347383521852</v>
       </c>
       <c r="F11" t="n">
         <v>1.347236682597893</v>
@@ -948,16 +1362,60 @@
         <v>0.4046302362888632</v>
       </c>
       <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.86458333333333</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.206371753246753</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.8104992378048781</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.171112804878049</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.9908060213414634</v>
+      <c r="M11" t="n">
+        <v>22.86458333333333</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15.82403273809524</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.589657738095238</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.428943452380953</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.619791666666667</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.373139880952381</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1426,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.532718619869126</v>
+        <v>3633.673469387755</v>
       </c>
       <c r="D12" t="n">
-        <v>17.20616775024228</v>
+        <v>335.9299417904445</v>
       </c>
       <c r="E12" t="n">
-        <v>12.77145135111925</v>
+        <v>249.347383521852</v>
       </c>
       <c r="F12" t="n">
         <v>1.347236682597893</v>
@@ -987,16 +1445,60 @@
         <v>0.4046302362888632</v>
       </c>
       <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22.86458333333333</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.206371753246753</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.8104992378048781</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.171112804878049</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.9908060213414634</v>
+      <c r="M12" t="n">
+        <v>22.86458333333333</v>
+      </c>
+      <c r="N12" t="n">
+        <v>15.82403273809524</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5.589657738095238</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.428943452380953</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.441592261904762</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.619791666666667</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.373139880952381</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="n">
+        <v>24.51525297619047</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1509,79 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.453599048185604</v>
+        <v>3603.514739229025</v>
       </c>
       <c r="D13" t="n">
-        <v>17.08493453409614</v>
+        <v>333.5630075704483</v>
       </c>
       <c r="E13" t="n">
-        <v>12.72512219591839</v>
+        <v>248.4428619203113</v>
       </c>
       <c r="F13" t="n">
         <v>1.342614575408649</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4069868759276986</v>
+        <v>0.4069868759276987</v>
       </c>
       <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.318824404761905</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22.19308035714286</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.76171875</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.8510861280487805</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.13671875</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.9939024390243902</v>
+      <c r="M13" t="n">
+        <v>22.19308035714286</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.61644345238095</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.280133928571428</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5.5859375</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.611235119047619</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.318824404761905</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.595610119047619</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.981026785714286</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>15.89704241071428</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1592,79 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.453599048185604</v>
+        <v>3603.514739229025</v>
       </c>
       <c r="D14" t="n">
-        <v>17.08493453409614</v>
+        <v>333.5630075704483</v>
       </c>
       <c r="E14" t="n">
-        <v>12.72512219591839</v>
+        <v>248.4428619203113</v>
       </c>
       <c r="F14" t="n">
         <v>1.342614575408649</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4069868759276986</v>
+        <v>0.4069868759276987</v>
       </c>
       <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.318824404761905</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22.19308035714286</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.76171875</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.8510861280487805</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.13671875</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.9939024390243902</v>
+      <c r="M14" t="n">
+        <v>22.19308035714286</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16.61644345238095</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.280133928571428</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5.5859375</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.611235119047619</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.318824404761905</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.595610119047619</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.981026785714286</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>4.45</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1675,79 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.453599048185604</v>
+        <v>3603.514739229025</v>
       </c>
       <c r="D15" t="n">
-        <v>17.08493453409614</v>
+        <v>333.5630075704483</v>
       </c>
       <c r="E15" t="n">
-        <v>12.72512219591839</v>
+        <v>248.4428619203113</v>
       </c>
       <c r="F15" t="n">
         <v>1.342614575408649</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4069868759276986</v>
+        <v>0.4069868759276987</v>
       </c>
       <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.318824404761905</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22.19308035714286</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.76171875</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.8510861280487805</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.13671875</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.9939024390243902</v>
+      <c r="M15" t="n">
+        <v>22.19308035714286</v>
+      </c>
+      <c r="N15" t="n">
+        <v>16.61644345238095</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.280133928571428</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5.5859375</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.611235119047619</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.318824404761905</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.595610119047619</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.981026785714286</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="n">
+        <v>5.079985119047619</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1758,79 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.361094586555621</v>
+        <v>3568.253968253968</v>
       </c>
       <c r="D16" t="n">
-        <v>16.85185284149356</v>
+        <v>329.0123650005885</v>
       </c>
       <c r="E16" t="n">
-        <v>12.5930681781071</v>
+        <v>245.86466442971</v>
       </c>
       <c r="F16" t="n">
         <v>1.338184833366527</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4142296496234834</v>
+        <v>0.4142296496234835</v>
       </c>
       <c r="H16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.155133928571429</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22.08705357142857</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.253405448717948</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.8350800304878049</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.131288109756098</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.9831840701219512</v>
+      <c r="M16" t="n">
+        <v>22.08705357142857</v>
+      </c>
+      <c r="N16" t="n">
+        <v>16.30394345238095</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.805803571428571</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5.169270833333333</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.449869791666666</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.155133928571429</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.3984375</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.729113520408163</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="n">
+        <v>4.146205357142857</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1841,79 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.361094586555621</v>
+        <v>3568.253968253968</v>
       </c>
       <c r="D17" t="n">
-        <v>16.85185284149356</v>
+        <v>329.0123650005885</v>
       </c>
       <c r="E17" t="n">
-        <v>12.5930681781071</v>
+        <v>245.86466442971</v>
       </c>
       <c r="F17" t="n">
         <v>1.338184833366527</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4142296496234834</v>
+        <v>0.4142296496234835</v>
       </c>
       <c r="H17" t="n">
+        <v>13</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.155133928571429</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22.08705357142857</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.253405448717948</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.8350800304878049</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.131288109756098</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.9831840701219512</v>
+      <c r="M17" t="n">
+        <v>22.08705357142857</v>
+      </c>
+      <c r="N17" t="n">
+        <v>16.30394345238095</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.805803571428571</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5.169270833333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.449869791666666</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.155133928571429</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.3984375</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.729113520408163</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="n">
+        <v>3.989955357142857</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1924,79 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.361094586555621</v>
+        <v>3568.253968253968</v>
       </c>
       <c r="D18" t="n">
-        <v>16.85185284149356</v>
+        <v>329.0123650005885</v>
       </c>
       <c r="E18" t="n">
-        <v>12.5930681781071</v>
+        <v>245.86466442971</v>
       </c>
       <c r="F18" t="n">
         <v>1.338184833366527</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4142296496234834</v>
+        <v>0.4142296496234835</v>
       </c>
       <c r="H18" t="n">
+        <v>13</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.155133928571429</v>
+      </c>
+      <c r="J18" t="n">
+        <v>22.08705357142857</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.253405448717948</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.8350800304878049</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.131288109756098</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.9831840701219512</v>
+      <c r="M18" t="n">
+        <v>22.08705357142857</v>
+      </c>
+      <c r="N18" t="n">
+        <v>16.30394345238095</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.805803571428571</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5.169270833333333</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.449869791666666</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.155133928571429</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.3984375</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.729113520408163</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="n">
+        <v>3.97047305764411</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +2007,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.262938726948246</v>
+        <v>3530.839002267574</v>
       </c>
       <c r="D19" t="n">
-        <v>16.77449741305374</v>
+        <v>327.5020923500969</v>
       </c>
       <c r="E19" t="n">
-        <v>12.48958913582127</v>
+        <v>243.8443593184153</v>
       </c>
       <c r="F19" t="n">
         <v>1.343078401589926</v>
@@ -1260,16 +2026,60 @@
         <v>0.4136753293416406</v>
       </c>
       <c r="H19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.11421130952381</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22.26190476190476</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.951636904761904</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.8557545731707318</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.140243902439025</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.9979992378048781</v>
+      <c r="M19" t="n">
+        <v>22.26190476190476</v>
+      </c>
+      <c r="N19" t="n">
+        <v>16.70758928571428</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.696056547619047</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.293154761904762</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.0234375</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.11421130952381</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.433035714285714</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.462319302721088</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="n">
+        <v>5.490973527568922</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2090,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.262938726948246</v>
+        <v>3530.839002267574</v>
       </c>
       <c r="D20" t="n">
-        <v>16.77449741305374</v>
+        <v>327.5020923500969</v>
       </c>
       <c r="E20" t="n">
-        <v>12.48958913582127</v>
+        <v>243.8443593184153</v>
       </c>
       <c r="F20" t="n">
         <v>1.343078401589926</v>
@@ -1299,16 +2109,60 @@
         <v>0.4136753293416406</v>
       </c>
       <c r="H20" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.11421130952381</v>
+      </c>
+      <c r="J20" t="n">
+        <v>22.26190476190476</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.951636904761904</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.8557545731707318</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.140243902439025</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.9979992378048781</v>
+      <c r="M20" t="n">
+        <v>22.26190476190476</v>
+      </c>
+      <c r="N20" t="n">
+        <v>16.70758928571428</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.696056547619047</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.293154761904762</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.0234375</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.11421130952381</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.433035714285714</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.462319302721088</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="n">
+        <v>4.534426887531328</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2173,79 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.134741225461035</v>
+        <v>3481.972789115646</v>
       </c>
       <c r="D21" t="n">
-        <v>16.82919597916487</v>
+        <v>328.570016736076</v>
       </c>
       <c r="E21" t="n">
-        <v>12.41815180313296</v>
+        <v>242.4496304421198</v>
       </c>
       <c r="F21" t="n">
         <v>1.355209393954988</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4053025882384034</v>
+        <v>0.4053025882384035</v>
       </c>
       <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.257440476190476</v>
+      </c>
+      <c r="J21" t="n">
+        <v>22.08705357142857</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.680958581349207</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.9094893292682927</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.131288109756098</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.020388719512195</v>
+      <c r="M21" t="n">
+        <v>22.08705357142857</v>
+      </c>
+      <c r="N21" t="n">
+        <v>17.75669642857143</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.079985119047619</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.146205357142857</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3.989955357142857</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.257440476190476</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.480282738095238</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.158801020408164</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="n">
+        <v>5.55</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2255,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="n">
+        <v>2.832961309523809</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2277,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>2.269345238095238</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2294,80 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>2.189360119047619</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>1.235532407407407</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>3.076946924603174</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>1.936939011715797</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/31/Filled_2D_sections/axial/week31_axial_Batch_Allmarks.xlsx
+++ b/measurements/31/Filled_2D_sections/axial/week31_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2373,4 +2579,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week31_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3615.992063492064</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.8241410510804</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3481.972789115646</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3682.426303854875</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>337.9985172464733</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.044813376617403</v>
+      </c>
+      <c r="E11" t="n">
+        <v>327.5020923500969</v>
+      </c>
+      <c r="F11" t="n">
+        <v>352.4191880226135</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.352331711908505</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01818050472385356</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.337554483277997</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.388034373384819</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3982754432903775</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01590030824626504</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3706114375641231</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4142296496234835</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>12</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>13</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>13</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>13</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>14</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>14</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>12</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.076055173697941</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.6048053188292994</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.234376040972246</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>40</v>
+      </c>
+      <c r="C48" t="n">
+        <v>20.20614769345238</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.932833038787463</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.44308035714286</v>
+      </c>
+      <c r="F48" t="n">
+        <v>29.51264880952381</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>89</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.530142288657035</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.610300601051451</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.696056547619047</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.03422619047619</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>111</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.940472838910339</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6607501817147486</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.11421130952381</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.761160714285714</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>